--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D2">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D3">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E3">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>426</v>
